--- a/缓存数据/infoPlow_Monitor_Citys.xlsx
+++ b/缓存数据/infoPlow_Monitor_Citys.xlsx
@@ -623,49 +623,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>125053.42</v>
+        <v>152341.24</v>
       </c>
       <c r="C4" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D4" t="n">
-        <v>1359.276304347826</v>
+        <v>1674.07956043956</v>
       </c>
       <c r="E4" t="n">
-        <v>30242.7</v>
+        <v>22985.36</v>
       </c>
       <c r="F4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G4" t="n">
-        <v>1591.721052631579</v>
+        <v>1094.540952380953</v>
       </c>
       <c r="H4" t="n">
-        <v>2094.84</v>
+        <v>4792.609999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J4" t="n">
-        <v>261.855</v>
+        <v>479.2609999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>65.18000000000001</v>
+        <v>95.73999999999999</v>
       </c>
       <c r="L4" t="n">
         <v>4</v>
       </c>
       <c r="M4" t="n">
-        <v>16.295</v>
+        <v>23.935</v>
       </c>
       <c r="N4" t="n">
-        <v>325059.7100000003</v>
+        <v>324895.5699999999</v>
       </c>
       <c r="O4" t="n">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="P4" t="n">
-        <v>880.9206233062339</v>
+        <v>864.0839627659573</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -677,13 +677,13 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>157456.1399999997</v>
+        <v>180214.95</v>
       </c>
       <c r="U4" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="V4" t="n">
-        <v>1280.131219512193</v>
+        <v>1430.277380952381</v>
       </c>
     </row>
     <row r="5">
@@ -693,49 +693,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>152341.24</v>
+        <v>165413.7200000001</v>
       </c>
       <c r="C5" t="n">
         <v>91</v>
       </c>
       <c r="D5" t="n">
-        <v>1674.07956043956</v>
+        <v>1817.733186813188</v>
       </c>
       <c r="E5" t="n">
-        <v>22985.36</v>
+        <v>35567.62</v>
       </c>
       <c r="F5" t="n">
         <v>21</v>
       </c>
       <c r="G5" t="n">
-        <v>1094.540952380953</v>
+        <v>1693.69619047619</v>
       </c>
       <c r="H5" t="n">
-        <v>4792.61</v>
+        <v>7672.1</v>
       </c>
       <c r="I5" t="n">
         <v>10</v>
       </c>
       <c r="J5" t="n">
-        <v>479.261</v>
+        <v>767.21</v>
       </c>
       <c r="K5" t="n">
-        <v>95.73999999999999</v>
+        <v>42.37</v>
       </c>
       <c r="L5" t="n">
         <v>4</v>
       </c>
       <c r="M5" t="n">
-        <v>23.935</v>
+        <v>10.5925</v>
       </c>
       <c r="N5" t="n">
-        <v>324895.5699999999</v>
+        <v>361294.62</v>
       </c>
       <c r="O5" t="n">
-        <v>376</v>
+        <v>398</v>
       </c>
       <c r="P5" t="n">
-        <v>864.0839627659572</v>
+        <v>907.7754271356783</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -747,13 +747,13 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>180214.9500000001</v>
+        <v>208695.8099999999</v>
       </c>
       <c r="U5" t="n">
         <v>126</v>
       </c>
       <c r="V5" t="n">
-        <v>1430.277380952382</v>
+        <v>1656.315952380952</v>
       </c>
     </row>
     <row r="6">
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>165413.7200000001</v>
+        <v>171589.62</v>
       </c>
       <c r="C6" t="n">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D6" t="n">
-        <v>1817.733186813188</v>
+        <v>2018.701411764706</v>
       </c>
       <c r="E6" t="n">
-        <v>35567.62</v>
+        <v>33005.23</v>
       </c>
       <c r="F6" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G6" t="n">
-        <v>1693.69619047619</v>
+        <v>1650.2615</v>
       </c>
       <c r="H6" t="n">
-        <v>7672.100000000001</v>
+        <v>7480.780000000001</v>
       </c>
       <c r="I6" t="n">
         <v>10</v>
       </c>
       <c r="J6" t="n">
-        <v>767.2100000000002</v>
+        <v>748.0780000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>42.37</v>
+        <v>116.89</v>
       </c>
       <c r="L6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>10.5925</v>
+        <v>38.96333333333333</v>
       </c>
       <c r="N6" t="n">
-        <v>361294.62</v>
+        <v>372461.6499999998</v>
       </c>
       <c r="O6" t="n">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="P6" t="n">
-        <v>907.7754271356783</v>
+        <v>975.0304973821985</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>208695.8100000001</v>
+        <v>212192.5200000002</v>
       </c>
       <c r="U6" t="n">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="V6" t="n">
-        <v>1656.315952380953</v>
+        <v>1798.241694915256</v>
       </c>
     </row>
     <row r="7">
@@ -833,49 +833,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>171589.62</v>
+        <v>156531.3999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D7" t="n">
-        <v>2018.701411764706</v>
+        <v>1820.132558139534</v>
       </c>
       <c r="E7" t="n">
-        <v>33005.23</v>
+        <v>22154.07</v>
       </c>
       <c r="F7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G7" t="n">
-        <v>1650.2615</v>
+        <v>1054.955714285714</v>
       </c>
       <c r="H7" t="n">
-        <v>7480.780000000001</v>
+        <v>5665.539999999998</v>
       </c>
       <c r="I7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J7" t="n">
-        <v>748.0780000000001</v>
+        <v>629.5044444444443</v>
       </c>
       <c r="K7" t="n">
-        <v>116.89</v>
+        <v>229.05</v>
       </c>
       <c r="L7" t="n">
         <v>3</v>
       </c>
       <c r="M7" t="n">
-        <v>38.96333333333333</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>372461.6499999998</v>
+        <v>332628.0399999999</v>
       </c>
       <c r="O7" t="n">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="P7" t="n">
-        <v>975.0304973821984</v>
+        <v>877.6465435356197</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -887,13 +887,13 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>212192.5200000003</v>
+        <v>184580.0600000001</v>
       </c>
       <c r="U7" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="V7" t="n">
-        <v>1798.241694915256</v>
+        <v>1551.092941176472</v>
       </c>
     </row>
     <row r="8">
@@ -903,49 +903,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>156531.3999999999</v>
+        <v>147293.1799999999</v>
       </c>
       <c r="C8" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="D8" t="n">
-        <v>1820.132558139534</v>
+        <v>1618.606373626372</v>
       </c>
       <c r="E8" t="n">
-        <v>22154.07</v>
+        <v>21143.17</v>
       </c>
       <c r="F8" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G8" t="n">
-        <v>1054.955714285714</v>
+        <v>1057.1585</v>
       </c>
       <c r="H8" t="n">
-        <v>5665.539999999999</v>
+        <v>3185.85</v>
       </c>
       <c r="I8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J8" t="n">
-        <v>629.5044444444443</v>
+        <v>318.585</v>
       </c>
       <c r="K8" t="n">
-        <v>229.05</v>
+        <v>232.92</v>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M8" t="n">
-        <v>76.34999999999999</v>
+        <v>58.23</v>
       </c>
       <c r="N8" t="n">
-        <v>332628.0399999999</v>
+        <v>311344.2099999999</v>
       </c>
       <c r="O8" t="n">
         <v>379</v>
       </c>
       <c r="P8" t="n">
-        <v>877.6465435356198</v>
+        <v>821.488680738786</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -957,13 +957,13 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>184580.0600000001</v>
+        <v>171855.1200000001</v>
       </c>
       <c r="U8" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="V8" t="n">
-        <v>1551.092941176471</v>
+        <v>1374.84096</v>
       </c>
     </row>
     <row r="9">
@@ -973,49 +973,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>147293.1799999999</v>
+        <v>153022.3299999999</v>
       </c>
       <c r="C9" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D9" t="n">
-        <v>1618.606373626372</v>
+        <v>1645.401397849461</v>
       </c>
       <c r="E9" t="n">
-        <v>21143.17</v>
+        <v>20944.87</v>
       </c>
       <c r="F9" t="n">
         <v>20</v>
       </c>
       <c r="G9" t="n">
-        <v>1057.1585</v>
+        <v>1047.2435</v>
       </c>
       <c r="H9" t="n">
-        <v>3185.849999999999</v>
+        <v>792.21</v>
       </c>
       <c r="I9" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J9" t="n">
-        <v>318.5849999999999</v>
+        <v>113.1728571428572</v>
       </c>
       <c r="K9" t="n">
-        <v>232.92</v>
+        <v>235.44</v>
       </c>
       <c r="L9" t="n">
         <v>4</v>
       </c>
       <c r="M9" t="n">
-        <v>58.23</v>
+        <v>58.86</v>
       </c>
       <c r="N9" t="n">
-        <v>311344.21</v>
+        <v>335440.7800000001</v>
       </c>
       <c r="O9" t="n">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="P9" t="n">
-        <v>821.4886807387862</v>
+        <v>860.1045641025643</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1027,13 +1027,13 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>171855.12</v>
+        <v>174994.8499999999</v>
       </c>
       <c r="U9" t="n">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="V9" t="n">
-        <v>1374.84096</v>
+        <v>1411.24879032258</v>
       </c>
     </row>
     <row r="10">
@@ -1043,49 +1043,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>153022.3299999999</v>
+        <v>162034.6300000001</v>
       </c>
       <c r="C10" t="n">
         <v>93</v>
       </c>
       <c r="D10" t="n">
-        <v>1645.401397849461</v>
+        <v>1742.307849462366</v>
       </c>
       <c r="E10" t="n">
-        <v>20944.87</v>
+        <v>27741.13</v>
       </c>
       <c r="F10" t="n">
         <v>20</v>
       </c>
       <c r="G10" t="n">
-        <v>1047.2435</v>
+        <v>1387.0565</v>
       </c>
       <c r="H10" t="n">
-        <v>792.21</v>
+        <v>296.7</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J10" t="n">
-        <v>113.1728571428572</v>
+        <v>49.45</v>
       </c>
       <c r="K10" t="n">
-        <v>235.44</v>
+        <v>229.52</v>
       </c>
       <c r="L10" t="n">
         <v>4</v>
       </c>
       <c r="M10" t="n">
-        <v>58.86</v>
+        <v>57.38</v>
       </c>
       <c r="N10" t="n">
-        <v>335440.7800000001</v>
+        <v>376177.4500000007</v>
       </c>
       <c r="O10" t="n">
-        <v>390</v>
+        <v>410</v>
       </c>
       <c r="P10" t="n">
-        <v>860.1045641025643</v>
+        <v>917.5059756097578</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1097,13 +1097,13 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>174994.8499999999</v>
+        <v>190301.9799999992</v>
       </c>
       <c r="U10" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="V10" t="n">
-        <v>1411.24879032258</v>
+        <v>1547.170569105685</v>
       </c>
     </row>
     <row r="11">
@@ -1113,49 +1113,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>162034.6300000001</v>
+        <v>162199.31</v>
       </c>
       <c r="C11" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D11" t="n">
-        <v>1742.307849462367</v>
+        <v>1725.524574468085</v>
       </c>
       <c r="E11" t="n">
-        <v>27741.13</v>
+        <v>38083.53000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G11" t="n">
-        <v>1387.0565</v>
+        <v>2004.396315789474</v>
       </c>
       <c r="H11" t="n">
-        <v>296.7</v>
+        <v>304.66</v>
       </c>
       <c r="I11" t="n">
         <v>6</v>
       </c>
       <c r="J11" t="n">
-        <v>49.45</v>
+        <v>50.77666666666666</v>
       </c>
       <c r="K11" t="n">
-        <v>229.52</v>
+        <v>248.07</v>
       </c>
       <c r="L11" t="n">
         <v>4</v>
       </c>
       <c r="M11" t="n">
-        <v>57.38</v>
+        <v>62.0175</v>
       </c>
       <c r="N11" t="n">
-        <v>376177.4500000005</v>
+        <v>407522.0399999998</v>
       </c>
       <c r="O11" t="n">
-        <v>410</v>
+        <v>382</v>
       </c>
       <c r="P11" t="n">
-        <v>917.5059756097572</v>
+        <v>1066.811623036649</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1167,13 +1167,13 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>190301.9799999995</v>
+        <v>200835.5700000002</v>
       </c>
       <c r="U11" t="n">
         <v>123</v>
       </c>
       <c r="V11" t="n">
-        <v>1547.170569105687</v>
+        <v>1632.809512195123</v>
       </c>
     </row>
   </sheetData>

--- a/缓存数据/infoPlow_Monitor_Citys.xlsx
+++ b/缓存数据/infoPlow_Monitor_Citys.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -81,18 +81,18 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -623,49 +623,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>152341.24</v>
+        <v>191541.05</v>
       </c>
       <c r="C4" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D4" t="n">
-        <v>1674.07956043956</v>
+        <v>2176.602840909091</v>
       </c>
       <c r="E4" t="n">
-        <v>22985.36</v>
+        <v>46107.50999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G4" t="n">
-        <v>1094.540952380953</v>
+        <v>1921.14625</v>
       </c>
       <c r="H4" t="n">
-        <v>4792.609999999999</v>
+        <v>389.89</v>
       </c>
       <c r="I4" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>479.2609999999999</v>
+        <v>97.4725</v>
       </c>
       <c r="K4" t="n">
-        <v>95.73999999999999</v>
+        <v>15.76</v>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>23.935</v>
+        <v>5.253333333333333</v>
       </c>
       <c r="N4" t="n">
-        <v>324895.5699999999</v>
+        <v>223773.99</v>
       </c>
       <c r="O4" t="n">
-        <v>376</v>
+        <v>334</v>
       </c>
       <c r="P4" t="n">
-        <v>864.0839627659573</v>
+        <v>669.9820059880238</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -677,13 +677,13 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>180214.95</v>
+        <v>238054.2100000001</v>
       </c>
       <c r="U4" t="n">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="V4" t="n">
-        <v>1430.277380952381</v>
+        <v>2000.455546218488</v>
       </c>
     </row>
     <row r="5">
@@ -693,49 +693,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>165413.7200000001</v>
+        <v>165798.1299999999</v>
       </c>
       <c r="C5" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="D5" t="n">
-        <v>1817.733186813188</v>
+        <v>1905.725632183907</v>
       </c>
       <c r="E5" t="n">
-        <v>35567.62</v>
+        <v>42186.25999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G5" t="n">
-        <v>1693.69619047619</v>
+        <v>1757.760833333333</v>
       </c>
       <c r="H5" t="n">
-        <v>7672.1</v>
+        <v>584.7</v>
       </c>
       <c r="I5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>767.21</v>
+        <v>146.175</v>
       </c>
       <c r="K5" t="n">
-        <v>42.37</v>
+        <v>30.93</v>
       </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M5" t="n">
-        <v>10.5925</v>
+        <v>10.31</v>
       </c>
       <c r="N5" t="n">
-        <v>361294.62</v>
+        <v>216338.59</v>
       </c>
       <c r="O5" t="n">
-        <v>398</v>
+        <v>316</v>
       </c>
       <c r="P5" t="n">
-        <v>907.7754271356783</v>
+        <v>684.6157911392406</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -747,13 +747,13 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>208695.8099999999</v>
+        <v>208600.02</v>
       </c>
       <c r="U5" t="n">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="V5" t="n">
-        <v>1656.315952380952</v>
+        <v>1767.796779661017</v>
       </c>
     </row>
     <row r="6">
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>171589.62</v>
+        <v>140688.33</v>
       </c>
       <c r="C6" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D6" t="n">
-        <v>2018.701411764706</v>
+        <v>1617.107241379311</v>
       </c>
       <c r="E6" t="n">
-        <v>33005.23</v>
+        <v>39842.50999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G6" t="n">
-        <v>1650.2615</v>
+        <v>1593.7004</v>
       </c>
       <c r="H6" t="n">
-        <v>7480.780000000001</v>
+        <v>351.44</v>
       </c>
       <c r="I6" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>748.0780000000001</v>
+        <v>87.86</v>
       </c>
       <c r="K6" t="n">
-        <v>116.89</v>
+        <v>21.98</v>
       </c>
       <c r="L6" t="n">
         <v>3</v>
       </c>
       <c r="M6" t="n">
-        <v>38.96333333333333</v>
+        <v>7.326666666666667</v>
       </c>
       <c r="N6" t="n">
-        <v>372461.6499999998</v>
+        <v>194591.0500000001</v>
       </c>
       <c r="O6" t="n">
-        <v>382</v>
+        <v>310</v>
       </c>
       <c r="P6" t="n">
-        <v>975.0304973821985</v>
+        <v>627.7130645161293</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -817,13 +817,13 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>212192.5200000002</v>
+        <v>180904.26</v>
       </c>
       <c r="U6" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="V6" t="n">
-        <v>1798.241694915256</v>
+        <v>1520.203865546218</v>
       </c>
     </row>
     <row r="7">
@@ -833,49 +833,49 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>156531.3999999999</v>
+        <v>177139.61</v>
       </c>
       <c r="C7" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D7" t="n">
-        <v>1820.132558139534</v>
+        <v>2108.804880952381</v>
       </c>
       <c r="E7" t="n">
-        <v>22154.07</v>
+        <v>49371.17999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G7" t="n">
-        <v>1054.955714285714</v>
+        <v>1974.8472</v>
       </c>
       <c r="H7" t="n">
-        <v>5665.539999999998</v>
+        <v>148.02</v>
       </c>
       <c r="I7" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>629.5044444444443</v>
+        <v>49.34</v>
       </c>
       <c r="K7" t="n">
-        <v>229.05</v>
+        <v>13.06</v>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>76.34999999999999</v>
+        <v>6.53</v>
       </c>
       <c r="N7" t="n">
-        <v>332628.0399999999</v>
+        <v>213596.4699999999</v>
       </c>
       <c r="O7" t="n">
-        <v>379</v>
+        <v>294</v>
       </c>
       <c r="P7" t="n">
-        <v>877.6465435356197</v>
+        <v>726.5186054421765</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -887,13 +887,13 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>184580.0600000001</v>
+        <v>226671.8700000001</v>
       </c>
       <c r="U7" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="V7" t="n">
-        <v>1551.092941176472</v>
+        <v>1988.349736842106</v>
       </c>
     </row>
     <row r="8">
@@ -903,49 +903,49 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>147293.1799999999</v>
+        <v>225728.6000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="D8" t="n">
-        <v>1618.606373626372</v>
+        <v>2752.787804878049</v>
       </c>
       <c r="E8" t="n">
-        <v>21143.17</v>
+        <v>47293.53999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G8" t="n">
-        <v>1057.1585</v>
+        <v>2056.240869565217</v>
       </c>
       <c r="H8" t="n">
-        <v>3185.85</v>
+        <v>80.7</v>
       </c>
       <c r="I8" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>318.585</v>
+        <v>40.35</v>
       </c>
       <c r="K8" t="n">
-        <v>232.92</v>
+        <v>2.67</v>
       </c>
       <c r="L8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M8" t="n">
-        <v>58.23</v>
+        <v>1.335</v>
       </c>
       <c r="N8" t="n">
-        <v>311344.2099999999</v>
+        <v>209518.89</v>
       </c>
       <c r="O8" t="n">
-        <v>379</v>
+        <v>280</v>
       </c>
       <c r="P8" t="n">
-        <v>821.488680738786</v>
+        <v>748.2817500000001</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -957,13 +957,13 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>171855.1200000001</v>
+        <v>273105.51</v>
       </c>
       <c r="U8" t="n">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="V8" t="n">
-        <v>1374.84096</v>
+        <v>2505.555137614679</v>
       </c>
     </row>
     <row r="9">
@@ -973,49 +973,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>153022.3299999999</v>
+        <v>177500.21</v>
       </c>
       <c r="C9" t="n">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D9" t="n">
-        <v>1645.401397849461</v>
+        <v>2063.955930232558</v>
       </c>
       <c r="E9" t="n">
-        <v>20944.87</v>
+        <v>37993.26</v>
       </c>
       <c r="F9" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G9" t="n">
-        <v>1047.2435</v>
+        <v>1651.880869565217</v>
       </c>
       <c r="H9" t="n">
-        <v>792.21</v>
+        <v>170.43</v>
       </c>
       <c r="I9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>113.1728571428572</v>
+        <v>56.81</v>
       </c>
       <c r="K9" t="n">
-        <v>235.44</v>
+        <v>19.65</v>
       </c>
       <c r="L9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>58.86</v>
+        <v>6.55</v>
       </c>
       <c r="N9" t="n">
-        <v>335440.7800000001</v>
+        <v>193661.6699999999</v>
       </c>
       <c r="O9" t="n">
-        <v>390</v>
+        <v>279</v>
       </c>
       <c r="P9" t="n">
-        <v>860.1045641025643</v>
+        <v>694.1278494623654</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1027,13 +1027,13 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>174994.8499999999</v>
+        <v>215683.55</v>
       </c>
       <c r="U9" t="n">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="V9" t="n">
-        <v>1411.24879032258</v>
+        <v>1875.509130434783</v>
       </c>
     </row>
     <row r="10">
@@ -1043,49 +1043,49 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>162034.6300000001</v>
+        <v>175788.4000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D10" t="n">
-        <v>1742.307849462366</v>
+        <v>2044.051162790699</v>
       </c>
       <c r="E10" t="n">
-        <v>27741.13</v>
+        <v>39194.35</v>
       </c>
       <c r="F10" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G10" t="n">
-        <v>1387.0565</v>
+        <v>1704.102173913043</v>
       </c>
       <c r="H10" t="n">
-        <v>296.7</v>
+        <v>1239.48</v>
       </c>
       <c r="I10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>49.45</v>
+        <v>309.87</v>
       </c>
       <c r="K10" t="n">
-        <v>229.52</v>
+        <v>7.91</v>
       </c>
       <c r="L10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M10" t="n">
-        <v>57.38</v>
+        <v>2.636666666666667</v>
       </c>
       <c r="N10" t="n">
-        <v>376177.4500000007</v>
+        <v>175431.2800000002</v>
       </c>
       <c r="O10" t="n">
-        <v>410</v>
+        <v>272</v>
       </c>
       <c r="P10" t="n">
-        <v>917.5059756097578</v>
+        <v>644.9679411764712</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1097,13 +1097,13 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>190301.9799999992</v>
+        <v>216230.1399999999</v>
       </c>
       <c r="U10" t="n">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="V10" t="n">
-        <v>1547.170569105685</v>
+        <v>1864.052931034482</v>
       </c>
     </row>
     <row r="11">
@@ -1113,49 +1113,49 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>162199.31</v>
+        <v>144934.3299999999</v>
       </c>
       <c r="C11" t="n">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="D11" t="n">
-        <v>1725.524574468085</v>
+        <v>1811.679124999999</v>
       </c>
       <c r="E11" t="n">
-        <v>38083.53000000001</v>
+        <v>43564.89999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G11" t="n">
-        <v>2004.396315789474</v>
+        <v>1980.222727272727</v>
       </c>
       <c r="H11" t="n">
-        <v>304.66</v>
+        <v>659.96</v>
       </c>
       <c r="I11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>50.77666666666666</v>
+        <v>164.99</v>
       </c>
       <c r="K11" t="n">
-        <v>248.07</v>
+        <v>26.23</v>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M11" t="n">
-        <v>62.0175</v>
+        <v>8.743333333333334</v>
       </c>
       <c r="N11" t="n">
-        <v>407522.0399999998</v>
+        <v>167602.8299999999</v>
       </c>
       <c r="O11" t="n">
-        <v>382</v>
+        <v>244</v>
       </c>
       <c r="P11" t="n">
-        <v>1066.811623036649</v>
+        <v>686.8968442622947</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1167,13 +1167,13 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>200835.5700000002</v>
+        <v>189185.4200000001</v>
       </c>
       <c r="U11" t="n">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="V11" t="n">
-        <v>1632.809512195123</v>
+        <v>1735.646055045872</v>
       </c>
     </row>
   </sheetData>
@@ -1186,6 +1186,6 @@
     <mergeCell ref="N1:P1"/>
     <mergeCell ref="Q1:S1"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>